--- a/projetos/_TEMPLATE_OBRA_NOVA/04_PRODUCAO_E_AVANCO/MATRIZ_BLOQUEIO_FVS_CONTRATOS_OBRA_NOVA.xlsx
+++ b/projetos/_TEMPLATE_OBRA_NOVA/04_PRODUCAO_E_AVANCO/MATRIZ_BLOQUEIO_FVS_CONTRATOS_OBRA_NOVA.xlsx
@@ -29,7 +29,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -47,13 +47,13 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001B365D"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00C5221F"/>
-      <sz val="9"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -117,16 +117,16 @@
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,10 +134,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
